--- a/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin. Papa dit : tu peux goûter une petite portion. Juste une petite bouchée. Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais. Benoît dit : c'est piquant, papa. Il a su nommer le goût. Papa sourit. Papa dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
+          <t>Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin. Tu peux goûter une petite portion. Juste une petite bouchée. Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais. C'est piquant, papa. Il a su nommer le goût. Papa sourit. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin.
+papa|Tu peux goûter une petite portion. Juste une petite bouchée.
+narrateur|Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais.
+enfant-m|C'est piquant, papa. Il a su nommer le goût. Papa sourit.
+papa|Merci d'avoir goûté.
+narrateur|Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Benoît goûte le radis. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Benoît a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Benoît boit une gorgée d'eau. Le radis reste à sa place.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Benoît goûte le radis. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,7 @@
           <t>narrateur|Benoît a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1844,7 @@
           <t>narrateur|Benoît boit une gorgée d'eau. Le radis reste à sa place.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le petit radis de Benoît</t>
+          <t>Les lanternes roses</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les bottes sèchent. Un peu de terre reste collée. Papa a des radis aux cheveux verts. Chouchou s'assoit. Il goûte. C'est piquant. Une petite bouchée suffit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin. Tu peux goûter une petite portion. Juste une petite bouchée. Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais. C'est piquant, papa. Il a su nommer le goût. Papa sourit. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
+          <t>Les bottes de Chouchou sèchent près de la porte. Un peu de terre est encore collée. Le robinet fait goutte, goutte. Dehors, le jardin sent la pluie d'hier. Les feuilles brillent encore. Chouchou vit ici, avec papa. Maman range le linge, tout près. Papa pose les radis dans l'évier. Les radis ont des cheveux verts. Ils sont roses, tout ronds. Papa, on dirait des lanternes ! Oui, Chouchou. De petites lanternes roses. On les lave ensemble ? Oui, papa. L'eau est froide. Elle coule sur les radis. La terre part tout doucement. Tu les poses sur le linge ? Chouchou pose les radis. Le linge est un peu rêche. Viens t'asseoir, maintenant. Chouchou va vers sa chaise. Il tire la chaise. Il s'assoit près de papa. Il pose les pieds sur la barre. Bravo, Chouchou. Tu es bien assis. On est ensemble, à table. Papa coupe un tout petit radis. Le radis croque sous le couteau. Un morceau rose attend dans l'assiette. À côté, il y a du pain. Tu as vu le petit cœur blanc ? Oui. Il brille. Ça sent le jardin, tout près. Tu veux goûter une petite portion ? Juste une petite bouchée. Chouchou prend un tout petit morceau. Il le met dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1329,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin.
-papa|Tu peux goûter une petite portion. Juste une petite bouchée.
-narrateur|Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais.
-enfant-m|C'est piquant, papa. Il a su nommer le goût. Papa sourit.
-papa|Merci d'avoir goûté.
-narrateur|Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.</t>
+          <t>narrateur|Les bottes de Chouchou sèchent près de la porte.
+narrateur|Un peu de terre est encore collée.
+narrateur|Le robinet fait goutte, goutte.
+narrateur|Dehors, le jardin sent la pluie d'hier.
+narrateur|Les feuilles brillent encore.
+narrateur|Chouchou vit ici, avec papa.
+narrateur|Maman range le linge, tout près.
+narrateur|Papa pose les radis dans l'évier.
+narrateur|Les radis ont des cheveux verts.
+narrateur|Ils sont roses, tout ronds.
+enfant-m|Papa, on dirait des lanternes !
+papa|Oui, Chouchou.
+papa|De petites lanternes roses.
+papa|On les lave ensemble ?
+enfant-m|Oui, papa.
+narrateur|L'eau est froide.
+narrateur|Elle coule sur les radis.
+narrateur|La terre part tout doucement.
+papa|Tu les poses sur le linge ?
+narrateur|Chouchou pose les radis.
+narrateur|Le linge est un peu rêche.
+papa|Viens t'asseoir, maintenant.
+narrateur|Chouchou va vers sa chaise.
+narrateur|Il tire la chaise.
+narrateur|Il s'assoit près de papa.
+narrateur|Il pose les pieds sur la barre.
+papa|Bravo, Chouchou.
+papa|Tu es bien assis.
+papa|On est ensemble, à table.
+narrateur|Papa coupe un tout petit radis.
+narrateur|Le radis croque sous le couteau.
+narrateur|Un morceau rose attend dans l'assiette.
+narrateur|À côté, il y a du pain.
+papa|Tu as vu le petit cœur blanc ?
+enfant-m|Oui. Il brille.
+narrateur|Ça sent le jardin, tout près.
+papa|Tu veux goûter une petite portion ?
+papa|Juste une petite bouchée.
+narrateur|Chouchou prend un tout petit morceau.
+narrateur|Il le met dans sa bouche.
+narrateur|Il goûte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>robinet,chaise</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Benoît goûte le radis. Que fait-il ?</t>
+          <t>Chouchou goûte le radis. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Benoît goûte le radis. Que fait-il ?</t>
+          <t>narrateur|Chouchou goûte le radis.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1533,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Benoît a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
+          <t>Chouchou mâche. Ça croque. Il mâche encore. C'est piquant, papa. C'est frais aussi. Oui. Piquant et frais. Bravo. Tu as nommé le goût. C'est du bon travail. Parce qu'il a goûté, Chouchou peut dire le goût. Un bout rose reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1730,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Benoît a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
+          <t>narrateur|Chouchou mâche.
+narrateur|Ça croque.
+narrateur|Il mâche encore.
+enfant-m|C'est piquant, papa.
+enfant-m|C'est frais aussi.
+papa|Oui. Piquant et frais.
+papa|Bravo. Tu as nommé le goût.
+papa|C'est du bon travail.
+narrateur|Parce qu'il a goûté, Chouchou peut dire le goût.
+narrateur|Un bout rose reste dans l'assiette.
+papa|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Benoît boit une gorgée d'eau. Le radis reste à sa place.</t>
+          <t>Chouchou pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Une petite portion, c'est déjà bien. Merci, papa. Merci, Chouchou. On range les lanternes, maintenant ? Oui. Chouchou aide. Les radis retrouvent le linge. Tu as fini de ranger les radis ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Chouchou reste avec papa. Le petit radis ne pique plus les mains.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1904,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Benoît boit une gorgée d'eau. Le radis reste à sa place.</t>
+          <t>narrateur|Chouchou pose le morceau.
+papa|Tu veux un peu d'eau ?
+narrateur|Il boit une gorgée d'eau.
+papa|Le reste peut attendre.
+papa|Une petite portion, c'est déjà bien.
+enfant-m|Merci, papa.
+papa|Merci, Chouchou.
+papa|On range les lanternes, maintenant ?
+enfant-m|Oui.
+narrateur|Chouchou aide.
+narrateur|Les radis retrouvent le linge.
+papa|Tu as fini de ranger les radis ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as bien aidé.
+narrateur|La cuisine est calme.
+papa|On reste un moment à table ?
+narrateur|Chouchou reste avec papa.
+narrateur|Le petit radis ne pique plus les mains.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Chouchou a encore le piquant sur la langue. C'était frais. Un petit morceau a suffi. Bravo, Chouchou. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2089,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Chouchou a encore le piquant sur la langue.
+enfant-m|C'était frais.
+papa|Un petit morceau a suffi.
+papa|Bravo, Chouchou.
+papa|On était assis, ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Benoît s'assoit à table près de papa. Dans l'assiette, il y a du pain et un petit radis rose. Le radis est croquant. Il sent le jardin. Papa dit : tu peux &lt;emphasis level="moderate"&gt;goûter&lt;/emphasis&gt; une petite portion. Juste une petite bouchée. Benoît prend un tout petit morceau. Il le met dans sa bouche. C'est un peu piquant. C'est frais. Benoît dit : c'est piquant, papa. Il a su nommer le goût. Papa sourit. Papa dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Parce qu'il a goûté, Benoît peut dire le goût. Il n'a pas besoin de tout finir. Le radis reste dans l'assiette.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les bottes de Chouchou sèchent près de la porte. Un peu de terre est encore collée. Le robinet fait goutte, goutte. Dehors, le jardin sent la pluie d'hier. Les feuilles brillent encore. Chouchou vit ici, avec papa. Maman range le linge, tout près. Papa pose les radis dans l'évier. Les radis ont des cheveux verts. Ils sont roses, tout ronds. Papa, on dirait des lanternes ! Oui, Chouchou. De petites lanternes roses. On les lave ensemble ? Oui, papa. L'eau est froide. Elle coule sur les radis. La terre part tout doucement. Tu les poses sur le linge ? Chouchou pose les radis. Le linge est un peu rêche. Viens t'asseoir, maintenant. Chouchou va vers sa chaise. Il tire la chaise. Il s'assoit près de papa. Il pose les pieds sur la barre. Bravo, Chouchou. Tu es bien assis. On est ensemble, à table. Papa coupe un tout petit radis. Le radis croque sous le couteau. Un morceau rose attend dans l'assiette. À côté, il y a du pain. Tu as vu le petit cœur blanc ? Oui. Il brille. Ça sent le jardin, tout près. Tu veux goûter une petite portion ? Juste une petite bouchée. Chouchou prend un tout petit morceau. Il le met dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Benoît goûte le radis. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou goûte le radis. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1561,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1586,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou mâche. Ça croque. Il mâche encore. C'est piquant, papa. C'est frais aussi. Oui. Piquant et frais. Bravo. Tu as nommé le goût. C'est du bon travail. Parce qu'il a goûté, Chouchou peut dire le goût. Un bout rose reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
+          <t>Chouchou mâche. Ça croque. Il mâche encore. C'est piquant, papa. C'est frais aussi. Oui. Piquant et frais. Bravo. Tu as nommé le goût. Parce qu'il a goûté, Chouchou peut dire le goût. Un bout rose reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Benoît a goûté. Il a nommé le goût. Une &lt;emphasis level="moderate"&gt;petite&lt;/emphasis&gt; portion, c'est assez. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou mâche. Ça croque. Il mâche encore. C'est piquant, papa. C'est frais aussi. Oui. Piquant et frais. Bravo. Tu as nommé le goût. Parce qu'il a goûté, Chouchou peut dire le goût. Un bout rose reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,13 +1736,11 @@
 enfant-m|C'est frais aussi.
 papa|Oui. Piquant et frais.
 papa|Bravo. Tu as nommé le goût.
-papa|C'est du bon travail.
 narrateur|Parce qu'il a goûté, Chouchou peut dire le goût.
 narrateur|Un bout rose reste dans l'assiette.
 papa|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1773,7 +1770,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Benoît boit une gorgée d'eau. Le radis reste à sa place.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Une petite portion, c'est déjà bien. Merci, papa. Merci, Chouchou. On range les lanternes, maintenant ? Oui. Chouchou aide. Les radis retrouvent le linge. Tu as fini de ranger les radis ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Chouchou reste avec papa. Le petit radis ne pique plus les mains.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,7 +1921,6 @@
 narrateur|Le petit radis ne pique plus les mains.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a encore le piquant sur la langue. C'était frais. Un petit morceau a suffi. Bravo, Chouchou. On était assis, ensemble. L'histoire est finie.</t>
+          <t>Chouchou a encore le piquant sur la langue. C'était frais. Un petit morceau a suffi. Bravo, Chouchou. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a encore le piquant sur la langue. C'était frais. Un petit morceau a suffi. Bravo, Chouchou. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,11 +2089,9 @@
 enfant-m|C'était frais.
 papa|Un petit morceau a suffi.
 papa|Bravo, Chouchou.
-papa|On était assis, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|On était assis, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2116,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-06.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Benoît, papa</t>
+          <t>Chouchou, papa</t>
         </is>
       </c>
     </row>
